--- a/Data/National Accounts/PSA-07IOS_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-07IOS_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8C262F-02DC-4FDD-AB5B-6A48DAD200A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BD6F23-F5CB-493C-A3D0-D18FC13BF400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IOS" sheetId="1" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -223,6 +220,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -667,7 +667,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -677,7 +677,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -877,10 +877,10 @@
         <v>390201.27925001539</v>
       </c>
       <c r="Z12" s="8">
-        <v>406845.48744039342</v>
+        <v>405932.1995417428</v>
       </c>
       <c r="AA12" s="8">
-        <v>397351.93417235144</v>
+        <v>407201.00575607829</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -1029,10 +1029,10 @@
         <v>100010.10423388844</v>
       </c>
       <c r="Z13" s="8">
-        <v>105001.18868307432</v>
+        <v>105059.22722972269</v>
       </c>
       <c r="AA13" s="8">
-        <v>110411.69487700476</v>
+        <v>110694.5839980556</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -1333,10 +1333,10 @@
         <v>19856.509394895242</v>
       </c>
       <c r="Z15" s="8">
-        <v>21333.540643867167</v>
+        <v>24058.486547291395</v>
       </c>
       <c r="AA15" s="8">
-        <v>23927.964952765284</v>
+        <v>26379.241148631558</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -1488,7 +1488,7 @@
         <v>126036.11521174925</v>
       </c>
       <c r="AA16" s="8">
-        <v>135648.61181064375</v>
+        <v>133212.77929505007</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -1637,10 +1637,10 @@
         <v>439870.2736023597</v>
       </c>
       <c r="Z17" s="8">
-        <v>450704.67790504789</v>
+        <v>454623.37597145652</v>
       </c>
       <c r="AA17" s="8">
-        <v>463384.42718479771</v>
+        <v>460390.34974113584</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -1789,10 +1789,10 @@
         <v>27064.549591538162</v>
       </c>
       <c r="Z18" s="8">
-        <v>28275.940478810578</v>
+        <v>28347.129746339058</v>
       </c>
       <c r="AA18" s="8">
-        <v>25194.93186706955</v>
+        <v>24501.271879943786</v>
       </c>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
@@ -1941,10 +1941,10 @@
         <v>103082.06824747362</v>
       </c>
       <c r="Z19" s="8">
-        <v>162276.554568705</v>
+        <v>155015.44269065917</v>
       </c>
       <c r="AA19" s="8">
-        <v>150877.60911132125</v>
+        <v>148094.32004090294</v>
       </c>
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
@@ -2191,10 +2191,10 @@
         <v>1993215.6433509516</v>
       </c>
       <c r="Z21" s="11">
-        <v>2313690.7465781914</v>
+        <v>2312289.2185855052</v>
       </c>
       <c r="AA21" s="11">
-        <v>2493052.062242595</v>
+        <v>2496728.4401264396</v>
       </c>
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="28" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:96" x14ac:dyDescent="0.2">
@@ -2518,7 +2518,7 @@
     </row>
     <row r="31" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:96" x14ac:dyDescent="0.2">
@@ -2718,10 +2718,10 @@
         <v>359921.48162211839</v>
       </c>
       <c r="Z37" s="8">
-        <v>362517.42909224523</v>
+        <v>361844.23657717789</v>
       </c>
       <c r="AA37" s="8">
-        <v>350025.1911444944</v>
+        <v>357551.0648457444</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -2870,10 +2870,10 @@
         <v>92147.590316263348</v>
       </c>
       <c r="Z38" s="8">
-        <v>92871.594461904213</v>
+        <v>92913.52194077782</v>
       </c>
       <c r="AA38" s="8">
-        <v>96901.868874645428</v>
+        <v>97040.303401872836</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -3025,7 +3025,7 @@
         <v>907271.62000598002</v>
       </c>
       <c r="AA39" s="8">
-        <v>1039833.491323573</v>
+        <v>1036412.7161374092</v>
       </c>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
@@ -3174,10 +3174,10 @@
         <v>18422.107292564047</v>
       </c>
       <c r="Z40" s="8">
-        <v>19057.731312379568</v>
+        <v>21505.092046478225</v>
       </c>
       <c r="AA40" s="8">
-        <v>21082.118141808198</v>
+        <v>23227.899795952319</v>
       </c>
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
@@ -3329,7 +3329,7 @@
         <v>112344.88028522229</v>
       </c>
       <c r="AA41" s="8">
-        <v>119252.87683264127</v>
+        <v>116846.36517594608</v>
       </c>
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
@@ -3478,10 +3478,10 @@
         <v>408414.60957547819</v>
       </c>
       <c r="Z42" s="8">
-        <v>407076.61180034454</v>
+        <v>410263.00554228493</v>
       </c>
       <c r="AA42" s="8">
-        <v>415302.88502485334</v>
+        <v>411975.45593942679</v>
       </c>
       <c r="AB42" s="9"/>
       <c r="AC42" s="9"/>
@@ -3630,10 +3630,10 @@
         <v>25015.887754260031</v>
       </c>
       <c r="Z43" s="8">
-        <v>25107.554001249991</v>
+        <v>25167.144186736285</v>
       </c>
       <c r="AA43" s="8">
-        <v>22084.488273259482</v>
+        <v>21498.983056131849</v>
       </c>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
@@ -3782,10 +3782,10 @@
         <v>91742.898170975241</v>
       </c>
       <c r="Z44" s="8">
-        <v>141409.42769081233</v>
+        <v>135369.04540099215</v>
       </c>
       <c r="AA44" s="8">
-        <v>129965.51287831966</v>
+        <v>127177.53469513703</v>
       </c>
       <c r="AB44" s="9"/>
       <c r="AC44" s="9"/>
@@ -4032,10 +4032,10 @@
         <v>1846837.8886618733</v>
       </c>
       <c r="Z46" s="11">
-        <v>2067656.8486501381</v>
+        <v>2066678.5459856498</v>
       </c>
       <c r="AA46" s="11">
-        <v>2194448.4324935949</v>
+        <v>2191730.3230476202</v>
       </c>
       <c r="AB46" s="9"/>
       <c r="AC46" s="9"/>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="53" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:96" x14ac:dyDescent="0.2">
@@ -4359,7 +4359,7 @@
     </row>
     <row r="56" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:96" x14ac:dyDescent="0.2">
@@ -4473,7 +4473,7 @@
         <v>51</v>
       </c>
       <c r="Z60" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA60" s="15"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>12.099177884304524</v>
       </c>
       <c r="Y62" s="16">
-        <v>4.2655442397239227</v>
+        <v>4.031488651693536</v>
       </c>
       <c r="Z62" s="16">
-        <v>-2.3334542378162411</v>
+        <v>0.31256604323772308</v>
       </c>
       <c r="AA62" s="16"/>
       <c r="AB62" s="9"/>
@@ -4699,10 +4699,10 @@
         <v>0.16486737547573682</v>
       </c>
       <c r="Y63" s="16">
-        <v>4.9905801892911512</v>
+        <v>5.048612872181522</v>
       </c>
       <c r="Z63" s="16">
-        <v>5.1528047080124111</v>
+        <v>5.3639807915307074</v>
       </c>
       <c r="AA63" s="16"/>
       <c r="AB63" s="9"/>
@@ -4989,10 +4989,10 @@
         <v>-2.5296557934688053</v>
       </c>
       <c r="Y65" s="16">
-        <v>7.4385241615106992</v>
+        <v>21.161711098509642</v>
       </c>
       <c r="Z65" s="16">
-        <v>12.161245768849653</v>
+        <v>9.6463033814628858</v>
       </c>
       <c r="AA65" s="16"/>
       <c r="AB65" s="9"/>
@@ -5137,7 +5137,7 @@
         <v>13.753110821970267</v>
       </c>
       <c r="Z66" s="16">
-        <v>7.6267795010540169</v>
+        <v>5.6941330437260405</v>
       </c>
       <c r="AA66" s="16"/>
       <c r="AB66" s="9"/>
@@ -5279,10 +5279,10 @@
         <v>19.334392584429565</v>
       </c>
       <c r="Y67" s="16">
-        <v>2.4630908140163257</v>
+        <v>3.3539666702809541</v>
       </c>
       <c r="Z67" s="16">
-        <v>2.8133165465882115</v>
+        <v>1.2685167711308907</v>
       </c>
       <c r="AA67" s="16"/>
       <c r="AB67" s="9"/>
@@ -5424,10 +5424,10 @@
         <v>-17.636550250484689</v>
       </c>
       <c r="Y68" s="16">
-        <v>4.4759321900969837</v>
+        <v>4.7389672991339893</v>
       </c>
       <c r="Z68" s="16">
-        <v>-10.896219752796114</v>
+        <v>-13.56700978479823</v>
       </c>
       <c r="AA68" s="16"/>
       <c r="AB68" s="9"/>
@@ -5569,10 +5569,10 @@
         <v>16.398462564489577</v>
       </c>
       <c r="Y69" s="16">
-        <v>57.424620331754113</v>
+        <v>50.380609669672936</v>
       </c>
       <c r="Z69" s="16">
-        <v>-7.0243945514369699</v>
+        <v>-4.464795590441696</v>
       </c>
       <c r="AA69" s="16"/>
       <c r="AB69" s="9"/>
@@ -5807,10 +5807,10 @@
         <v>32.46983904442871</v>
       </c>
       <c r="Y71" s="16">
-        <v>16.078295607216077</v>
+        <v>16.007980686832951</v>
       </c>
       <c r="Z71" s="16">
-        <v>7.7521732724940904</v>
+        <v>7.9764771663711258</v>
       </c>
       <c r="AA71" s="16"/>
       <c r="AB71" s="9"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="78" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:91" x14ac:dyDescent="0.2">
@@ -6120,7 +6120,7 @@
     </row>
     <row r="81" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:91" x14ac:dyDescent="0.2">
@@ -6234,7 +6234,7 @@
         <v>51</v>
       </c>
       <c r="Z85" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA85" s="15"/>
     </row>
@@ -6315,10 +6315,10 @@
         <v>6.7683147122742753</v>
       </c>
       <c r="Y87" s="16">
-        <v>0.72125382970398277</v>
+        <v>0.53421511447271541</v>
       </c>
       <c r="Z87" s="16">
-        <v>-3.4459689232133712</v>
+        <v>-1.18646956271688</v>
       </c>
       <c r="AA87" s="16"/>
       <c r="AB87" s="9"/>
@@ -6460,10 +6460,10 @@
         <v>-4.7833708266644948</v>
       </c>
       <c r="Y88" s="16">
-        <v>0.7857005735646112</v>
+        <v>0.83120092656324118</v>
       </c>
       <c r="Z88" s="16">
-        <v>4.3396201347597412</v>
+        <v>4.4415294726696288</v>
       </c>
       <c r="AA88" s="16"/>
       <c r="AB88" s="9"/>
@@ -6608,7 +6608,7 @@
         <v>21.116390997498797</v>
       </c>
       <c r="Z89" s="16">
-        <v>14.61104573255794</v>
+        <v>14.234005923229248</v>
       </c>
       <c r="AA89" s="16"/>
       <c r="AB89" s="9"/>
@@ -6750,10 +6750,10 @@
         <v>-6.7833954917356891</v>
       </c>
       <c r="Y90" s="16">
-        <v>3.4503328512915914</v>
+        <v>16.735244806432121</v>
       </c>
       <c r="Z90" s="16">
-        <v>10.622391491654739</v>
+        <v>8.0111619413236923</v>
       </c>
       <c r="AA90" s="16"/>
       <c r="AB90" s="9"/>
@@ -6898,7 +6898,7 @@
         <v>10.052902185184493</v>
       </c>
       <c r="Z91" s="16">
-        <v>6.148919763749717</v>
+        <v>4.0068447082727516</v>
       </c>
       <c r="AA91" s="16"/>
       <c r="AB91" s="9"/>
@@ -7040,10 +7040,10 @@
         <v>13.499207793216101</v>
       </c>
       <c r="Y92" s="16">
-        <v>-0.32760771621866525</v>
+        <v>0.45257831709987784</v>
       </c>
       <c r="Z92" s="16">
-        <v>2.0208169632067978</v>
+        <v>0.41740307412760558</v>
       </c>
       <c r="AA92" s="16"/>
       <c r="AB92" s="9"/>
@@ -7185,10 +7185,10 @@
         <v>-20.285178944845086</v>
       </c>
       <c r="Y93" s="16">
-        <v>0.36643211662297404</v>
+        <v>0.60464147409877</v>
       </c>
       <c r="Z93" s="16">
-        <v>-12.040462913432364</v>
+        <v>-14.575198136853558</v>
       </c>
       <c r="AA93" s="16"/>
       <c r="AB93" s="9"/>
@@ -7330,10 +7330,10 @@
         <v>10.219463576489801</v>
       </c>
       <c r="Y94" s="16">
-        <v>54.136647642498531</v>
+        <v>47.552615079494984</v>
       </c>
       <c r="Z94" s="16">
-        <v>-8.0927523711604721</v>
+        <v>-6.051243607126068</v>
       </c>
       <c r="AA94" s="16"/>
       <c r="AB94" s="9"/>
@@ -7568,10 +7568,10 @@
         <v>25.672248571807586</v>
       </c>
       <c r="Y96" s="16">
-        <v>11.956596804945292</v>
+        <v>11.903625037878228</v>
       </c>
       <c r="Z96" s="16">
-        <v>6.132138605408926</v>
+        <v>6.0508576578042721</v>
       </c>
       <c r="AA96" s="16"/>
       <c r="AB96" s="9"/>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="102" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="1:96" x14ac:dyDescent="0.2">
@@ -7878,7 +7878,7 @@
     </row>
     <row r="105" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:96" x14ac:dyDescent="0.2">
@@ -8078,10 +8078,10 @@
         <v>108.41288980347323</v>
       </c>
       <c r="Z111" s="16">
-        <v>112.22784197139073</v>
+        <v>112.18423799743495</v>
       </c>
       <c r="AA111" s="16">
-        <v>113.52095341284165</v>
+        <v>113.88611188495663</v>
       </c>
       <c r="AB111" s="9"/>
       <c r="AC111" s="9"/>
@@ -8230,10 +8230,10 @@
         <v>108.53252254414885</v>
       </c>
       <c r="Z112" s="16">
-        <v>113.06060727335272</v>
+        <v>113.07205349151054</v>
       </c>
       <c r="AA112" s="16">
-        <v>113.94176000860826</v>
+        <v>114.07073155948031</v>
       </c>
       <c r="AB112" s="9"/>
       <c r="AC112" s="9"/>
@@ -8385,7 +8385,7 @@
         <v>111.67738737819941</v>
       </c>
       <c r="AA113" s="16">
-        <v>114.08123494432681</v>
+        <v>114.45777051903383</v>
       </c>
       <c r="AB113" s="9"/>
       <c r="AC113" s="9"/>
@@ -8534,10 +8534,10 @@
         <v>107.78630848008457</v>
       </c>
       <c r="Z114" s="16">
-        <v>111.94165923626636</v>
+        <v>111.87344139376204</v>
       </c>
       <c r="AA114" s="16">
-        <v>113.49886568235026</v>
+        <v>113.56705246863683</v>
       </c>
       <c r="AB114" s="9"/>
       <c r="AC114" s="9"/>
@@ -8689,7 +8689,7 @@
         <v>112.18679025850355</v>
       </c>
       <c r="AA115" s="16">
-        <v>113.74871232751235</v>
+        <v>114.006780693999</v>
       </c>
       <c r="AB115" s="9"/>
       <c r="AC115" s="9"/>
@@ -8838,10 +8838,10 @@
         <v>107.70189491007133</v>
       </c>
       <c r="Z116" s="16">
-        <v>110.71740916574721</v>
+        <v>110.81266646758368</v>
       </c>
       <c r="AA116" s="16">
-        <v>111.57746403737767</v>
+        <v>111.75188791072728</v>
       </c>
       <c r="AB116" s="9"/>
       <c r="AC116" s="9"/>
@@ -8990,10 +8990,10 @@
         <v>108.18944287487562</v>
       </c>
       <c r="Z117" s="16">
-        <v>112.61925585185577</v>
+        <v>112.63546446115529</v>
       </c>
       <c r="AA117" s="16">
-        <v>114.08429099793216</v>
+        <v>113.96479459504312</v>
       </c>
       <c r="AB117" s="9"/>
       <c r="AC117" s="9"/>
@@ -9142,10 +9142,10 @@
         <v>112.35972516953446</v>
       </c>
       <c r="Z118" s="16">
-        <v>114.75653159668961</v>
+        <v>114.51321255274436</v>
       </c>
       <c r="AA118" s="16">
-        <v>116.09049644776192</v>
+        <v>116.44691839317885</v>
       </c>
       <c r="AB118" s="9"/>
       <c r="AC118" s="9"/>
@@ -9392,10 +9392,10 @@
         <v>107.92585833265183</v>
       </c>
       <c r="Z120" s="16">
-        <v>111.89916489714797</v>
+        <v>111.88431907211374</v>
       </c>
       <c r="AA120" s="16">
-        <v>113.607229284932</v>
+        <v>113.91585971465305</v>
       </c>
       <c r="AB120" s="9"/>
       <c r="AC120" s="9"/>
@@ -9513,7 +9513,7 @@
     </row>
     <row r="127" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="129" spans="1:96" x14ac:dyDescent="0.2">
@@ -9523,7 +9523,7 @@
     </row>
     <row r="130" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131" spans="1:96" x14ac:dyDescent="0.2">
@@ -9723,10 +9723,10 @@
         <v>19.576470842563591</v>
       </c>
       <c r="Z136" s="17">
-        <v>17.584263931646582</v>
+        <v>17.55542499956227</v>
       </c>
       <c r="AA136" s="17">
-        <v>15.938372896028424</v>
+        <v>16.309383079541355</v>
       </c>
       <c r="AB136" s="9"/>
       <c r="AC136" s="9"/>
@@ -9875,10 +9875,10 @@
         <v>5.0175255531184568</v>
       </c>
       <c r="Z137" s="17">
-        <v>4.5382551163488349</v>
+        <v>4.5435158536954336</v>
       </c>
       <c r="AA137" s="17">
-        <v>4.4287761394635794</v>
+        <v>4.4335852557697386</v>
       </c>
       <c r="AB137" s="9"/>
       <c r="AC137" s="9"/>
@@ -10027,10 +10027,10 @@
         <v>40.253191439218114</v>
       </c>
       <c r="Z138" s="17">
-        <v>43.792250245415495</v>
+        <v>43.818793665714459</v>
       </c>
       <c r="AA138" s="17">
-        <v>47.582435450608287</v>
+        <v>47.512371357718301</v>
       </c>
       <c r="AB138" s="9"/>
       <c r="AC138" s="9"/>
@@ -10179,10 +10179,10 @@
         <v>0.99620477398586449</v>
       </c>
       <c r="Z139" s="17">
-        <v>0.92205670422541053</v>
+        <v>1.040461822591928</v>
       </c>
       <c r="AA139" s="17">
-        <v>0.95978601149793763</v>
+        <v>1.0565522755568748</v>
       </c>
       <c r="AB139" s="9"/>
       <c r="AC139" s="9"/>
@@ -10331,10 +10331,10 @@
         <v>5.5587537999655963</v>
       </c>
       <c r="Z140" s="17">
-        <v>5.447405423484061</v>
+        <v>5.4507072125194274</v>
       </c>
       <c r="AA140" s="17">
-        <v>5.4410661479978346</v>
+        <v>5.3354933261505959</v>
       </c>
       <c r="AB140" s="9"/>
       <c r="AC140" s="9"/>
@@ -10483,10 +10483,10 @@
         <v>22.068373538492764</v>
       </c>
       <c r="Z141" s="17">
-        <v>19.479901476531072</v>
+        <v>19.661181322705076</v>
       </c>
       <c r="AA141" s="17">
-        <v>18.587033708713079</v>
+        <v>18.439744681156462</v>
       </c>
       <c r="AB141" s="9"/>
       <c r="AC141" s="9"/>
@@ -10635,10 +10635,10 @@
         <v>1.3578334929199041</v>
       </c>
       <c r="Z142" s="17">
-        <v>1.2221140842020042</v>
+        <v>1.2259335691440807</v>
       </c>
       <c r="AA142" s="17">
-        <v>1.0106059255098649</v>
+        <v>0.9813350737777069</v>
       </c>
       <c r="AB142" s="9"/>
       <c r="AC142" s="9"/>
@@ -10787,10 +10787,10 @@
         <v>5.1716465597357164</v>
       </c>
       <c r="Z143" s="17">
-        <v>7.0137530181465344</v>
+        <v>6.7039815540672993</v>
       </c>
       <c r="AA143" s="17">
-        <v>6.0519237201810023</v>
+        <v>5.9315349503289641</v>
       </c>
       <c r="AB143" s="9"/>
       <c r="AC143" s="9"/>
@@ -11354,7 +11354,7 @@
     </row>
     <row r="152" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="154" spans="1:96" x14ac:dyDescent="0.2">
@@ -11364,7 +11364,7 @@
     </row>
     <row r="155" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="156" spans="1:96" x14ac:dyDescent="0.2">
@@ -11564,10 +11564,10 @@
         <v>19.488525973598016</v>
       </c>
       <c r="Z161" s="17">
-        <v>17.532765619639125</v>
+        <v>17.508491452627215</v>
       </c>
       <c r="AA161" s="17">
-        <v>15.950486052057913</v>
+        <v>16.31364320171318</v>
       </c>
       <c r="AB161" s="9"/>
       <c r="AC161" s="9"/>
@@ -11716,10 +11716,10 @@
         <v>4.9894790919103844</v>
       </c>
       <c r="Z162" s="17">
-        <v>4.4916347953256883</v>
+        <v>4.4957897357213374</v>
       </c>
       <c r="AA162" s="17">
-        <v>4.4157733414830771</v>
+        <v>4.427565854312653</v>
       </c>
       <c r="AB162" s="9"/>
       <c r="AC162" s="9"/>
@@ -11868,10 +11868,10 @@
         <v>40.560717519618414</v>
       </c>
       <c r="Z163" s="17">
-        <v>43.879216253813532</v>
+        <v>43.899987338054061</v>
       </c>
       <c r="AA163" s="17">
-        <v>47.38473121202442</v>
+        <v>47.287419681097816</v>
       </c>
       <c r="AB163" s="9"/>
       <c r="AC163" s="9"/>
@@ -12020,10 +12020,10 @@
         <v>0.99749455031550116</v>
       </c>
       <c r="Z164" s="17">
-        <v>0.92170668091377617</v>
+        <v>1.0405629887749146</v>
       </c>
       <c r="AA164" s="17">
-        <v>0.96070237193280372</v>
+        <v>1.0597973460372496</v>
       </c>
       <c r="AB164" s="9"/>
       <c r="AC164" s="9"/>
@@ -12172,10 +12172,10 @@
         <v>5.5274269328939667</v>
       </c>
       <c r="Z165" s="17">
-        <v>5.4334393232883986</v>
+        <v>5.4360113479400471</v>
       </c>
       <c r="AA165" s="17">
-        <v>5.4342984353991808</v>
+        <v>5.3312382434655632</v>
       </c>
       <c r="AB165" s="9"/>
       <c r="AC165" s="9"/>
@@ -12324,10 +12324,10 @@
         <v>22.114264174610099</v>
       </c>
       <c r="Z166" s="17">
-        <v>19.687822573949006</v>
+        <v>19.851321645506339</v>
       </c>
       <c r="AA166" s="17">
-        <v>18.925160367196987</v>
+        <v>18.796813257872497</v>
       </c>
       <c r="AB166" s="9"/>
       <c r="AC166" s="9"/>
@@ -12476,10 +12476,10 @@
         <v>1.3545253705177827</v>
       </c>
       <c r="Z167" s="17">
-        <v>1.2142998494958852</v>
+        <v>1.217758041550359</v>
       </c>
       <c r="AA167" s="17">
-        <v>1.0063799151645794</v>
+        <v>0.9809137022951494</v>
       </c>
       <c r="AB167" s="9"/>
       <c r="AC167" s="9"/>
@@ -12628,10 +12628,10 @@
         <v>4.9675663865358297</v>
       </c>
       <c r="Z168" s="17">
-        <v>6.8391149035745915</v>
+        <v>6.5500774498257215</v>
       </c>
       <c r="AA168" s="17">
-        <v>5.9224683047410362</v>
+        <v>5.8026087132058999</v>
       </c>
       <c r="AB168" s="9"/>
       <c r="AC168" s="9"/>
